--- a/data/source/customer.xlsx
+++ b/data/source/customer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\easyexcelcomparator\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BBDB36D-E7E4-4E13-BD5A-9D30BD85A8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E545E2-7630-401C-8322-AA69B4D55EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{49010DB3-58E0-4DBF-ADA8-C1E2291ECC60}"/>
   </bookViews>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6605A4E-8B79-4106-92C3-0B944BF1B2AB}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A2:E5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
@@ -427,77 +427,77 @@
     <col min="3" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>30</v>
-      </c>
-      <c r="C2" s="2">
-        <f t="shared" ref="C2:D4" ca="1" si="0">NOW()</f>
-        <v>46284.754507407408</v>
-      </c>
-      <c r="D2" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>46284.754507407408</v>
-      </c>
-      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>30</v>
       </c>
       <c r="C3" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>46284.754507407408</v>
+        <f t="shared" ref="C3:D5" ca="1" si="0">NOW()</f>
+        <v>46294.912096412037</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46284.754507407408</v>
+        <v>46294.912096412037</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>30</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46284.754507407408</v>
+        <v>46294.912096412037</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46284.754507407408</v>
+        <v>46294.912096412037</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>46294.912096412037</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>46294.912096412037</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
     </row>

--- a/data/source/customer.xlsx
+++ b/data/source/customer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\easyexcelcomparator\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47E545E2-7630-401C-8322-AA69B4D55EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379EB52D-5E36-4644-A438-62FC6E81FF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{49010DB3-58E0-4DBF-ADA8-C1E2291ECC60}"/>
   </bookViews>
@@ -54,10 +54,10 @@
     <t>abbc1</t>
   </si>
   <si>
-    <t>abbc2</t>
-  </si>
-  <si>
     <t>abbc3</t>
+  </si>
+  <si>
+    <t>abbc</t>
   </si>
 </sst>
 </file>
@@ -453,11 +453,11 @@
       </c>
       <c r="C3" s="2">
         <f t="shared" ref="C3:D5" ca="1" si="0">NOW()</f>
-        <v>46294.912096412037</v>
+        <v>46294.981105671293</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46294.912096412037</v>
+        <v>46294.981105671293</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -465,18 +465,18 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>30</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46294.912096412037</v>
+        <v>46294.981105671293</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46294.912096412037</v>
+        <v>46294.981105671293</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -484,18 +484,18 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>30</v>
       </c>
       <c r="C5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46294.912096412037</v>
+        <v>46294.981105671293</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46294.912096412037</v>
+        <v>46294.981105671293</v>
       </c>
       <c r="E5">
         <v>3</v>
